--- a/data/hr_data.xlsx
+++ b/data/hr_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thun/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{136805B0-029C-CF4F-A64D-478F64055705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{323F2659-A1C3-B142-B4D1-CF7CDB2B3F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{CCD9E7E3-E957-BB4C-A8A6-925AF086ED34}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17680" xr2:uid="{CCD9E7E3-E957-BB4C-A8A6-925AF086ED34}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
   <si>
     <t>Staff Name</t>
   </si>
@@ -76,9 +76,6 @@
     <t>LOE 2025 (Average)</t>
   </si>
   <si>
-    <t>Haha Haha</t>
-  </si>
-  <si>
     <t>REALM Manager</t>
   </si>
   <si>
@@ -94,9 +91,6 @@
     <t>11618M</t>
   </si>
   <si>
-    <t>Hehe Hehe</t>
-  </si>
-  <si>
     <t>USAID DCA</t>
   </si>
   <si>
@@ -109,9 +103,6 @@
     <t>DRC code</t>
   </si>
   <si>
-    <t>Hoho Hoho</t>
-  </si>
-  <si>
     <t>Meal Coordinator</t>
   </si>
   <si>
@@ -125,6 +116,21 @@
   </si>
   <si>
     <t>BRACE</t>
+  </si>
+  <si>
+    <t>Duch Panhathun</t>
+  </si>
+  <si>
+    <t>Chhorn Sotheavann</t>
+  </si>
+  <si>
+    <t>Outh Chhayly</t>
+  </si>
+  <si>
+    <t>Heng Bunkheang</t>
+  </si>
+  <si>
+    <t>Project Coordinator</t>
   </si>
 </sst>
 </file>
@@ -134,7 +140,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d\-mmm\-yyyy"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -144,6 +150,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -226,8 +239,9 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -235,14 +249,15 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="15" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="16">
     <dxf>
@@ -973,7 +988,7 @@
         <v>7</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>11</v>
@@ -984,78 +999,78 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="6">
+        <v>43831</v>
+      </c>
+      <c r="D2" s="6">
+        <v>45658</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="7">
-        <v>43831</v>
-      </c>
-      <c r="D2" s="7">
-        <v>45658</v>
-      </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="7">
+      <c r="G2" s="6">
         <v>44197</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="6">
         <v>45930</v>
       </c>
       <c r="I2" s="2">
         <v>1161051</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" s="6">
+        <v>16</v>
+      </c>
+      <c r="K2" s="5">
         <v>84002328</v>
       </c>
       <c r="L2" s="4">
         <v>840023280001</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="N2" s="5">
+        <v>17</v>
+      </c>
+      <c r="N2" s="9">
         <v>0.04</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="7">
+      <c r="C3" s="6">
         <v>43832</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="6">
         <v>45659</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="7">
+        <v>15</v>
+      </c>
+      <c r="G3" s="6">
         <v>44563</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="6">
         <v>45931</v>
       </c>
       <c r="I3" s="2">
         <v>1161046</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K3" s="4">
         <v>84008754</v>
@@ -1064,42 +1079,42 @@
         <v>840023280001</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="N3" s="5">
+        <v>17</v>
+      </c>
+      <c r="N3" s="9">
         <v>0.39</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="6">
+        <v>43833</v>
+      </c>
+      <c r="D4" s="6">
+        <v>45660</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="7">
-        <v>43833</v>
-      </c>
-      <c r="D4" s="7">
-        <v>45660</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="7">
+      <c r="G4" s="6">
         <v>44564</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="6">
         <v>45932</v>
       </c>
       <c r="I4" s="2">
         <v>1161045</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K4" s="4">
         <v>84008753</v>
@@ -1108,42 +1123,42 @@
         <v>840023280001</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="N4" s="5">
+        <v>17</v>
+      </c>
+      <c r="N4" s="9">
         <v>0.88</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="7">
+        <v>31</v>
+      </c>
+      <c r="C5" s="6">
         <v>43834</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="6">
         <v>45658</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5" s="7">
+        <v>24</v>
+      </c>
+      <c r="G5" s="6">
         <v>44565</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="6">
         <v>45933</v>
       </c>
       <c r="I5" s="2">
         <v>1161044</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K5" s="4">
         <v>84008752</v>
@@ -1152,16 +1167,16 @@
         <v>840023280001</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="N5" s="5">
+        <v>17</v>
+      </c>
+      <c r="N5" s="9">
         <v>0.02</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" s="8"/>
+      <c r="A6" s="7"/>
       <c r="B6" s="2"/>
-      <c r="C6" s="7"/>
+      <c r="C6" s="6"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -1172,7 +1187,7 @@
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="2"/>
-      <c r="N6" s="9"/>
+      <c r="N6" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/hr_data.xlsx
+++ b/data/hr_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thun/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{323F2659-A1C3-B142-B4D1-CF7CDB2B3F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87CE765B-C4B3-A849-A082-DD5761BEE254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17680" xr2:uid="{CCD9E7E3-E957-BB4C-A8A6-925AF086ED34}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="37">
   <si>
     <t>Staff Name</t>
   </si>
@@ -131,6 +131,21 @@
   </si>
   <si>
     <t>Project Coordinator</t>
+  </si>
+  <si>
+    <t>Data analysis, impact evaluation, M&amp;E frameworks, report writing, project management, stakeholder engagement, leadership, software tools</t>
+  </si>
+  <si>
+    <t>Research methodologies, statistical analysis, data visualization, qualitative, survey design, impact assessment, writing reports</t>
+  </si>
+  <si>
+    <t>Data collection, database management, indicator tracking, performance monitoring, community feedback mechanisms, report writing, knowledge of M&amp;E software</t>
+  </si>
+  <si>
+    <t>Project planning, budget management, stakeholder coordination, communication, problem-solving, risk management, reporting</t>
+  </si>
+  <si>
+    <t>Skill</t>
   </si>
 </sst>
 </file>
@@ -176,7 +191,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -238,12 +253,34 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -254,12 +291,36 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="17">
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <numFmt numFmtId="13" formatCode="0%"/>
       <fill>
@@ -616,23 +677,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C82FCDB5-7CBD-4745-A01C-775620CB9213}" name="Table3" displayName="Table3" ref="A1:N6" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
-  <autoFilter ref="A1:N6" xr:uid="{C82FCDB5-7CBD-4745-A01C-775620CB9213}"/>
-  <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{D14A9C78-83B4-0C40-B0DC-0A118F586954}" name="Staff Name" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{B0D1EC4C-5BF0-A244-B9B1-4DFD8838B655}" name="Role" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{801C0434-85F3-D440-B189-63C4D9208B28}" name="Staff Start Date" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{28AF4ED1-5D81-E642-B9A8-16EFEC0A4608}" name="Staff End Date" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{E323FB7D-450E-8449-99A2-EE8966AB5F09}" name="Award/SOF Name (Informal)" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{8AFAD3F1-357B-A747-92CE-6186A7E96807}" name="Status of Award" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{AED3CE18-61F0-0D45-8751-DB43DDAD7C2E}" name="Project Start Date" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{65F384ED-65D7-A44C-AD66-3F5C4322653C}" name="Project End Date" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{518E7E82-2A93-BD46-949B-D7A894E92964}" name="Project#" dataDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{2EF5B298-FEDF-4D43-8630-2CEFD2780A18}" name="Activity" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{86C04B2C-2060-7647-AC94-1A4BD70D61BB}" name="Award/SOF Code" dataDxfId="3"/>
-    <tableColumn id="15" xr3:uid="{B9EC93E4-F44E-FA46-9391-6E60B1B63F2D}" name="DRC code" dataDxfId="2"/>
-    <tableColumn id="12" xr3:uid="{975B7E92-BFF5-2546-A852-581ABF927352}" name="Cost Center" dataDxfId="1"/>
-    <tableColumn id="13" xr3:uid="{FFC9ADCE-96D6-A347-8794-3CEF63D2D7F0}" name="LOE 2025 (Average)" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C82FCDB5-7CBD-4745-A01C-775620CB9213}" name="Table3" displayName="Table3" ref="A1:O6" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A1:O6" xr:uid="{C82FCDB5-7CBD-4745-A01C-775620CB9213}"/>
+  <tableColumns count="15">
+    <tableColumn id="1" xr3:uid="{D14A9C78-83B4-0C40-B0DC-0A118F586954}" name="Staff Name" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{B0D1EC4C-5BF0-A244-B9B1-4DFD8838B655}" name="Role" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{801C0434-85F3-D440-B189-63C4D9208B28}" name="Staff Start Date" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{28AF4ED1-5D81-E642-B9A8-16EFEC0A4608}" name="Staff End Date" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{E323FB7D-450E-8449-99A2-EE8966AB5F09}" name="Award/SOF Name (Informal)" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{8AFAD3F1-357B-A747-92CE-6186A7E96807}" name="Status of Award" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{AED3CE18-61F0-0D45-8751-DB43DDAD7C2E}" name="Project Start Date" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{65F384ED-65D7-A44C-AD66-3F5C4322653C}" name="Project End Date" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{518E7E82-2A93-BD46-949B-D7A894E92964}" name="Project#" dataDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{2EF5B298-FEDF-4D43-8630-2CEFD2780A18}" name="Activity" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{86C04B2C-2060-7647-AC94-1A4BD70D61BB}" name="Award/SOF Code" dataDxfId="4"/>
+    <tableColumn id="15" xr3:uid="{B9EC93E4-F44E-FA46-9391-6E60B1B63F2D}" name="DRC code" dataDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{975B7E92-BFF5-2546-A852-581ABF927352}" name="Cost Center" dataDxfId="2"/>
+    <tableColumn id="13" xr3:uid="{FFC9ADCE-96D6-A347-8794-3CEF63D2D7F0}" name="LOE 2025 (Average)" dataDxfId="1"/>
+    <tableColumn id="14" xr3:uid="{560B8F1B-E6CD-7F48-88EC-99A42B87C29F}" name="Skill" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -935,7 +997,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AF048E7-BABB-214A-B1A3-3C7862A70428}">
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17" customWidth="1"/>
@@ -950,10 +1012,10 @@
     <col min="12" max="12" width="17.5" customWidth="1"/>
     <col min="13" max="13" width="12.83203125" customWidth="1"/>
     <col min="14" max="14" width="15.33203125" customWidth="1"/>
-    <col min="15" max="15" width="19.5" customWidth="1"/>
+    <col min="15" max="15" width="131.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -996,8 +1058,11 @@
       <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="O1" s="12" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>27</v>
       </c>
@@ -1040,8 +1105,11 @@
       <c r="N2" s="9">
         <v>0.04</v>
       </c>
+      <c r="O2" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>28</v>
       </c>
@@ -1084,8 +1152,11 @@
       <c r="N3" s="9">
         <v>0.39</v>
       </c>
+      <c r="O3" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>29</v>
       </c>
@@ -1128,8 +1199,11 @@
       <c r="N4" s="9">
         <v>0.88</v>
       </c>
+      <c r="O4" s="10" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>30</v>
       </c>
@@ -1170,10 +1244,13 @@
         <v>17</v>
       </c>
       <c r="N5" s="9">
-        <v>0.02</v>
+        <v>0.2</v>
+      </c>
+      <c r="O5" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="7"/>
       <c r="B6" s="2"/>
       <c r="C6" s="6"/>
@@ -1188,6 +1265,7 @@
       <c r="L6" s="4"/>
       <c r="M6" s="2"/>
       <c r="N6" s="8"/>
+      <c r="O6" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/hr_data.xlsx
+++ b/data/hr_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thun/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thun/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87CE765B-C4B3-A849-A082-DD5761BEE254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A3D0580-0D04-A843-B8D5-9EAC4C149A1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17680" xr2:uid="{CCD9E7E3-E957-BB4C-A8A6-925AF086ED34}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="38">
   <si>
     <t>Staff Name</t>
   </si>
@@ -79,9 +79,6 @@
     <t>REALM Manager</t>
   </si>
   <si>
-    <t>FCF USAID</t>
-  </si>
-  <si>
     <t>Active</t>
   </si>
   <si>
@@ -91,9 +88,6 @@
     <t>11618M</t>
   </si>
   <si>
-    <t>USAID DCA</t>
-  </si>
-  <si>
     <t>Evaluation Specialist</t>
   </si>
   <si>
@@ -109,9 +103,6 @@
     <t>GG</t>
   </si>
   <si>
-    <t>Likely</t>
-  </si>
-  <si>
     <t>1161045PM08A</t>
   </si>
   <si>
@@ -146,6 +137,18 @@
   </si>
   <si>
     <t>Skill</t>
+  </si>
+  <si>
+    <t>FCF</t>
+  </si>
+  <si>
+    <t>USAID</t>
+  </si>
+  <si>
+    <t>DCA</t>
+  </si>
+  <si>
+    <t>RPP</t>
   </si>
 </sst>
 </file>
@@ -191,7 +194,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -228,10 +231,10 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -244,20 +247,18 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -271,7 +272,20 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -280,7 +294,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -288,12 +302,14 @@
     <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="15" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -677,8 +693,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C82FCDB5-7CBD-4745-A01C-775620CB9213}" name="Table3" displayName="Table3" ref="A1:O6" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
-  <autoFilter ref="A1:O6" xr:uid="{C82FCDB5-7CBD-4745-A01C-775620CB9213}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C82FCDB5-7CBD-4745-A01C-775620CB9213}" name="Table3" displayName="Table3" ref="A1:O8" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A1:O8" xr:uid="{C82FCDB5-7CBD-4745-A01C-775620CB9213}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{D14A9C78-83B4-0C40-B0DC-0A118F586954}" name="Staff Name" dataDxfId="14"/>
     <tableColumn id="2" xr3:uid="{B0D1EC4C-5BF0-A244-B9B1-4DFD8838B655}" name="Role" dataDxfId="13"/>
@@ -997,9 +1013,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AF048E7-BABB-214A-B1A3-3C7862A70428}">
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="16.5" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
     <col min="3" max="3" width="18.5" customWidth="1"/>
     <col min="4" max="4" width="16.5" customWidth="1"/>
@@ -1050,7 +1067,7 @@
         <v>7</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>11</v>
@@ -1058,13 +1075,13 @@
       <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="12" t="s">
-        <v>36</v>
+      <c r="O1" s="9" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>13</v>
@@ -1073,13 +1090,13 @@
         <v>43831</v>
       </c>
       <c r="D2" s="6">
-        <v>45658</v>
+        <v>46023</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>15</v>
       </c>
       <c r="G2" s="6">
         <v>44197</v>
@@ -1091,7 +1108,7 @@
         <v>1161051</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K2" s="5">
         <v>84002328</v>
@@ -1100,33 +1117,33 @@
         <v>840023280001</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N2" s="9">
+        <v>16</v>
+      </c>
+      <c r="N2" s="7">
         <v>0.04</v>
       </c>
       <c r="O2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C3" s="6">
         <v>43832</v>
       </c>
       <c r="D3" s="6">
-        <v>45659</v>
+        <v>46024</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G3" s="6">
         <v>44563</v>
@@ -1138,7 +1155,7 @@
         <v>1161046</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K3" s="4">
         <v>84008754</v>
@@ -1147,33 +1164,33 @@
         <v>840023280001</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N3" s="9">
+        <v>16</v>
+      </c>
+      <c r="N3" s="7">
         <v>0.39</v>
       </c>
       <c r="O3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C4" s="6">
         <v>43833</v>
       </c>
       <c r="D4" s="6">
-        <v>45660</v>
+        <v>46025</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G4" s="6">
         <v>44564</v>
@@ -1185,7 +1202,7 @@
         <v>1161045</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K4" s="4">
         <v>84008753</v>
@@ -1194,33 +1211,33 @@
         <v>840023280001</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N4" s="9">
-        <v>0.88</v>
-      </c>
-      <c r="O4" s="10" t="s">
-        <v>34</v>
+        <v>16</v>
+      </c>
+      <c r="N4" s="7">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C5" s="6">
         <v>43834</v>
       </c>
       <c r="D5" s="6">
-        <v>45658</v>
+        <v>46023</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G5" s="6">
         <v>44565</v>
@@ -1232,7 +1249,7 @@
         <v>1161044</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K5" s="4">
         <v>84008752</v>
@@ -1241,31 +1258,155 @@
         <v>840023280001</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N5" s="9">
+        <v>16</v>
+      </c>
+      <c r="N5" s="7">
         <v>0.2</v>
       </c>
       <c r="O5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A6" s="7"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="11"/>
+      <c r="A6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="6">
+        <v>43831</v>
+      </c>
+      <c r="D6" s="6">
+        <v>46023</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="6">
+        <v>44197</v>
+      </c>
+      <c r="H6" s="6">
+        <v>45930</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1161051</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K6" s="5">
+        <v>84002328</v>
+      </c>
+      <c r="L6" s="4">
+        <v>840023280001</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N6" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="O6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="6">
+        <v>43833</v>
+      </c>
+      <c r="D7" s="6">
+        <v>46025</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="6">
+        <v>44564</v>
+      </c>
+      <c r="H7" s="6">
+        <v>45932</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1161045</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="4">
+        <v>84008753</v>
+      </c>
+      <c r="L7" s="4">
+        <v>840023280001</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N7" s="7">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="O7" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A8" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="12">
+        <v>43834</v>
+      </c>
+      <c r="D8" s="12">
+        <v>46023</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="12">
+        <v>44565</v>
+      </c>
+      <c r="H8" s="12">
+        <v>45933</v>
+      </c>
+      <c r="I8" s="12">
+        <v>1161044</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="K8" s="13">
+        <v>84008752</v>
+      </c>
+      <c r="L8" s="13">
+        <v>840023280001</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="N8" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="O8" s="14" t="s">
+        <v>32</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
